--- a/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>20.3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>20.2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>20.8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>20.9</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>23.4</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>20.6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>20.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>23.4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>19.6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>20.1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>20.2</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -777,8 +777,8 @@
       <c r="C28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>4</v>
+      <c r="D28">
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>22.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>23.1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26">
-        <v>20.2</v>
+      <c r="D26" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:4">
